--- a/public/exports-with-coowners/29188386.xlsx
+++ b/public/exports-with-coowners/29188386.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311468820</t>
+          <t xml:space="preserve">311468821</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416780</t>
+          <t xml:space="preserve">311468976</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311469035</t>
+          <t xml:space="preserve">311469044</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">

--- a/public/exports-with-coowners/29188386.xlsx
+++ b/public/exports-with-coowners/29188386.xlsx
@@ -2014,12 +2014,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311468821</t>
+          <t xml:space="preserve">311468820</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M27" t="inlineStr">

--- a/public/exports-with-coowners/29188386.xlsx
+++ b/public/exports-with-coowners/29188386.xlsx
@@ -5914,7 +5914,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311468976</t>
+          <t xml:space="preserve">311416780</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311469044</t>
+          <t xml:space="preserve">311469035</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
